--- a/KatalonData/RADTestData/Summary.xlsx
+++ b/KatalonData/RADTestData/Summary.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="767">
   <si>
     <t>Result</t>
   </si>
@@ -2143,6 +2143,210 @@
   </si>
   <si>
     <t>Thu Aug 06 17:26:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:21:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:22:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:23:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:24:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:25:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:26:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:26:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:27:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:28:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:29:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:29:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:30:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:31:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:32:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:33:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:34:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:36:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:37:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:38:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:38:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:39:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:40:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:41:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:42:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:43:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:44:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:44:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:45:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:46:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:47:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:49:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:51:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:52:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:53:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:54:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:54:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:55:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:56:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:57:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:58:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:58:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 13:59:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:01:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:02:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:03:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:03:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:04:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:05:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:06:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:07:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:07:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:08:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:09:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:11:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:12:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:12:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:14:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:14:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:15:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:16:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:17:00 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3471,7 +3675,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>631</v>
+        <v>699</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3494,7 +3698,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>632</v>
+        <v>700</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3517,7 +3721,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>633</v>
+        <v>701</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3540,7 +3744,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>634</v>
+        <v>702</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3563,7 +3767,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>635</v>
+        <v>703</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3586,7 +3790,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>636</v>
+        <v>704</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -3609,7 +3813,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>637</v>
+        <v>705</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -3632,7 +3836,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>638</v>
+        <v>706</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -3655,7 +3859,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>639</v>
+        <v>707</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -3678,7 +3882,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>640</v>
+        <v>708</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -3701,7 +3905,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>641</v>
+        <v>709</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -3724,7 +3928,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>642</v>
+        <v>710</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -3747,7 +3951,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>643</v>
+        <v>711</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -3770,7 +3974,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>644</v>
+        <v>712</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -3793,7 +3997,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>645</v>
+        <v>713</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -3813,10 +4017,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>646</v>
+        <v>714</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -3845,7 +4049,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>647</v>
+        <v>715</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -3871,10 +4075,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>648</v>
+        <v>716</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -3903,7 +4107,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>649</v>
+        <v>717</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -3923,10 +4127,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>650</v>
+        <v>718</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -3955,7 +4159,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>651</v>
+        <v>719</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -3984,7 +4188,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>652</v>
+        <v>720</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -4010,7 +4214,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>653</v>
+        <v>721</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -4036,10 +4240,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>654</v>
+        <v>722</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -4068,7 +4272,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>655</v>
+        <v>723</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -4094,10 +4298,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>656</v>
+        <v>724</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -4123,7 +4327,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>657</v>
+        <v>725</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -4152,7 +4356,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>658</v>
+        <v>726</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -4181,7 +4385,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>659</v>
+        <v>727</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -4207,10 +4411,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>660</v>
+        <v>728</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -4239,7 +4443,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>661</v>
+        <v>729</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -4262,7 +4466,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>662</v>
+        <v>730</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -4291,7 +4495,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>663</v>
+        <v>731</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -4320,7 +4524,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>664</v>
+        <v>732</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -4346,7 +4550,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>665</v>
+        <v>733</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -4375,7 +4579,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>666</v>
+        <v>734</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -4401,10 +4605,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>667</v>
+        <v>735</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -4430,10 +4634,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>668</v>
+        <v>736</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -4459,7 +4663,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>669</v>
+        <v>737</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -4488,7 +4692,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>670</v>
+        <v>738</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -4517,7 +4721,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>671</v>
+        <v>739</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -4546,7 +4750,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>672</v>
+        <v>740</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -4575,7 +4779,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>673</v>
+        <v>741</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -4595,10 +4799,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>674</v>
+        <v>742</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -4627,7 +4831,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>675</v>
+        <v>743</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -4656,7 +4860,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>676</v>
+        <v>744</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -4682,7 +4886,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>677</v>
+        <v>745</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -4711,7 +4915,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>678</v>
+        <v>746</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -4740,7 +4944,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>679</v>
+        <v>747</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -4766,10 +4970,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>680</v>
+        <v>748</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -4795,7 +4999,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>681</v>
+        <v>749</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -4824,7 +5028,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>682</v>
+        <v>750</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -4844,10 +5048,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>683</v>
+        <v>751</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -4893,7 +5097,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>684</v>
+        <v>752</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -4916,7 +5120,7 @@
         <v>35</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>685</v>
+        <v>753</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -4962,7 +5166,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>686</v>
+        <v>754</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -4985,7 +5189,7 @@
         <v>35</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>687</v>
+        <v>755</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -5031,7 +5235,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>688</v>
+        <v>756</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -5057,7 +5261,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>689</v>
+        <v>757</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -5080,10 +5284,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>690</v>
+        <v>758</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -5259,7 +5463,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>691</v>
+        <v>759</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -5279,7 +5483,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>692</v>
+        <v>760</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -5296,10 +5500,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>693</v>
+        <v>761</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -5319,7 +5523,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>694</v>
+        <v>762</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -5336,10 +5540,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>695</v>
+        <v>763</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -5359,7 +5563,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>696</v>
+        <v>764</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -5376,10 +5580,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>697</v>
+        <v>765</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -5396,10 +5600,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>698</v>
+        <v>766</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>

--- a/KatalonData/RADTestData/Summary.xlsx
+++ b/KatalonData/RADTestData/Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAEFF54-5F6C-438D-AA3E-93352391360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427D4B8E-2E89-4017-82F0-5EF9E9A3EEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="11325" activeTab="5" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="2152" yWindow="2602" windowWidth="21600" windowHeight="11326" activeTab="1" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="172">
   <si>
     <t>Result</t>
   </si>
@@ -240,261 +240,6 @@
     <t>2026</t>
   </si>
   <si>
-    <t>Thu Jun 25 00:14:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:14:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:15:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:15:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:16:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:21:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:21:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:21:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:22:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:22:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:22:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:22:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:23:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:23:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:23:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:23:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:23:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:24:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:24:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:24:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:24:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:24:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:25:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:29:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:29:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:29:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:30:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:30:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:30:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:30:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:32:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:32:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:32:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:33:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:33:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:33:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:34:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:34:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:34:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:35:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:35:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:35:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:36:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:36:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:37:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:37:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:37:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:38:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:38:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:39:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:39:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:39:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:40:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:40:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:41:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:41:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:41:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:42:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:42:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:42:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:42:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:43:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:43:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:43:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:44:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:44:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:45:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:45:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:46:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:46:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:46:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:48:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:48:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:48:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:48:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:49:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:49:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:49:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:49:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:50:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:50:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:51:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:51:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 15:01:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 15:02:13 EDT 2026</t>
-  </si>
-  <si>
     <t>MFInsNum</t>
   </si>
   <si>
@@ -504,1652 +249,325 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>Thu Jul 09 14:23:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 14:23:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 14:23:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 14:23:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 14:24:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 14:24:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 14:25:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 15:06:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 13:00:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 13:00:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 14:37:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 14:37:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 14:37:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 14:38:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 14:38:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 14:39:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 14:39:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 21:14:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 21:14:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 21:14:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:28:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:29:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:29:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:29:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:30:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:30:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:31:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:31:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:32:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:33:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:34:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:34:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:34:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:35:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:35:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:36:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:36:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:36:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:37:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:37:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:37:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:38:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:38:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:39:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:39:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:39:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:39:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:40:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:40:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:41:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:41:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:42:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:42:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:43:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:43:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:44:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:45:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:45:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:46:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:46:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:46:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:47:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:47:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:48:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:48:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:49:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:49:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:50:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:50:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:50:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:51:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:51:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:51:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:51:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:52:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:52:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:52:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:53:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:53:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:54:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:55:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:55:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:56:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:56:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:56:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:57:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:57:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:58:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:58:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:58:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:59:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:59:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 21:59:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:00:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:00:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:00:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:00:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:01:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:01:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:02:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:02:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:02:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:02:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:03:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:03:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:03:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:03:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:04:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:04:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:04:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:05:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:06:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:06:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:07:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:07:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:08:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:08:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:08:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:08:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:09:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:09:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:09:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:10:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:10:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:11:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:11:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:11:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:12:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:13:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:13:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:13:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:14:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:14:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:15:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:15:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:15:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:16:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:16:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:17:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:17:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:17:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:18:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:18:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:19:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:20:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:20:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:21:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:21:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:21:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:22:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:22:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:22:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:23:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:23:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:23:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:24:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:24:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:24:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:25:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:25:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:25:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:26:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:26:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:26:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:27:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:27:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:27:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:28:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:29:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:29:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:30:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:31:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:31:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:32:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:33:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:33:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:33:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:34:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:34:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:35:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:35:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:35:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:36:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:36:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:37:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:37:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:37:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:38:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:38:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:38:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:39:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:39:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:39:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:40:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:40:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:40:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:41:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:41:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:41:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:42:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:42:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:42:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:43:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:43:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:44:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:44:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:44:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:45:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:45:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:45:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:46:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:46:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:46:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:47:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:47:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:47:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:48:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:48:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:48:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:49:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:49:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:50:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:50:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:50:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:51:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:51:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:51:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:52:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:52:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:53:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:53:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:53:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:54:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:54:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:54:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:55:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:55:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:55:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:56:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:56:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:56:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:57:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:57:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:57:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:58:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:59:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:59:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 22:59:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:00:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:00:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:00:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:01:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:01:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:02:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:02:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:02:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:03:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:03:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:03:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:04:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:04:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:04:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:05:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:06:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:06:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:06:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:07:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:07:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:07:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:08:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:08:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:08:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:09:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:09:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:09:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:10:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:10:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:10:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:11:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:11:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:11:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:12:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:12:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:12:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:13:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:13:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:14:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:14:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:15:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:15:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:16:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:17:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:17:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:18:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:18:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:18:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:19:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:19:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:19:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:20:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:20:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:21:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:21:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:22:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:22:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:23:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:23:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:24:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:24:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:25:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:25:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:25:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:26:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:27:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:27:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:28:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:28:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:28:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:29:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:29:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:29:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:30:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:30:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:31:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:31:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:31:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:32:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:32:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:32:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:33:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:33:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:33:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:34:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:34:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:34:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:35:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:35:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:35:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:36:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:36:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:37:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:37:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:38:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:38:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:39:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:39:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:39:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:40:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:41:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:41:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:41:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:42:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:42:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:43:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:44:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:44:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:45:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:45:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:45:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:46:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:46:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:46:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:47:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:48:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:48:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:49:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:49:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:49:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:50:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:50:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:51:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:51:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:52:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:52:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:52:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:53:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:53:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:53:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:54:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:54:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:54:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:55:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:55:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:55:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:56:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:56:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:57:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:57:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:57:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:58:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:58:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 23:59:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:00:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:00:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:01:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:01:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:01:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:01:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:02:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:02:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:03:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:03:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:04:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:04:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:04:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:04:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:04:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:05:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:06:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:06:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:06:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:07:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:07:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:07:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:08:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:08:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:08:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:08:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:09:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:09:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:10:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:11:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:11:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:12:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:12:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:13:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:13:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:14:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:15:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:16:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:16:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:17:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:17:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:18:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:19:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:20:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 00:21:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:18:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:19:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:19:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:19:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:19:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:20:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:20:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:21:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:21:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:22:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:22:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:23:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:23:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:24:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:24:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:25:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:25:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:25:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:25:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:26:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:26:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:27:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:27:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:28:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:28:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:29:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:30:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 16:31:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:42:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:42:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:43:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:43:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:43:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:43:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:44:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:44:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:44:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:45:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:46:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:46:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:46:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 04 17:47:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:56:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:57:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:57:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:57:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:58:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:58:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:58:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:59:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:59:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 16:59:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:00:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:00:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:00:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:01:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:01:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:01:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:02:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:03:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:03:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:04:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:05:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:05:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:05:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:06:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:06:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:07:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:08:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:08:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:08:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:09:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:09:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:10:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:10:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:10:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:11:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:11:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:11:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:12:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:13:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:14:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:14:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:14:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:15:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:15:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:16:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:16:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:16:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:17:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:17:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:17:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:18:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:19:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:19:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:20:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:21:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:21:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:21:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:22:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:22:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:22:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:23:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:23:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:24:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:24:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:25:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:25:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:26:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 17:26:47 EDT 2026</t>
+    <t>Thu Sep 03 18:38:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:39:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:39:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:40:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:41:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:41:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:42:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:43:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:45:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:45:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:46:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:46:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:46:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:47:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:47:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:48:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:49:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:49:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:50:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:50:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:51:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:52:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:52:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:52:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:53:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:53:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:53:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:54:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:54:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:54:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:55:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:55:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:55:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:56:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:56:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:56:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:57:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:58:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:58:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:58:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:59:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 18:59:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:00:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:00:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:00:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:01:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:02:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:02:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:02:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:03:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:04:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:05:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:05:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:06:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:07:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:07:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:08:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:08:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:08:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:09:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:09:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:10:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:10:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:11:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:11:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:12:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:12:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:13:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:13:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:14:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:14:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:14:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:15:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:15:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:15:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:16:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:16:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:16:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:17:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:17:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:17:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:18:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:18:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:18:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:19:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:19:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:19:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:20:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:21:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:21:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:21:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:22:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:23:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:24:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 19:24:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:15:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:16:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:17:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:17:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:25:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:35:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:36:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:36:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:39:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:40:45 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2522,16 +940,16 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="40.19921875" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="9.19921875" style="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="40.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2565,7 +983,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>624</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2588,10 +1006,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>625</v>
+        <v>163</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2617,7 +1035,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>626</v>
+        <v>164</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2643,7 +1061,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>627</v>
+        <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2669,7 +1087,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>628</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2692,10 +1110,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>629</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2721,7 +1139,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>630</v>
+        <v>165</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2754,16 +1172,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.06640625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="51.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="29.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17.06640625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="51.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="18" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="52.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2797,7 +1215,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>254</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2817,7 +1235,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>255</v>
+        <v>167</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2837,7 +1255,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>256</v>
+        <v>71</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2857,7 +1275,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>257</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2877,7 +1295,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2897,7 +1315,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>259</v>
+        <v>170</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2920,7 +1338,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>260</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2940,10 +1358,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>261</v>
+        <v>168</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2963,10 +1381,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>262</v>
+        <v>169</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2989,7 +1407,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>263</v>
+        <v>166</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -3006,10 +1424,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -3029,7 +1447,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -3049,10 +1467,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -3075,7 +1493,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -3095,7 +1513,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -3118,7 +1536,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>269</v>
+        <v>171</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -3138,10 +1556,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -3175,7 +1593,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -3223,16 +1641,16 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="24.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="48.46484375" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="35" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="48.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -3263,10 +1681,10 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3289,10 +1707,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3315,7 +1733,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3335,10 +1753,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>293</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3358,10 +1776,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>294</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3381,10 +1799,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>295</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -3416,19 +1834,19 @@
   <dimension ref="A1:L64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="30.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="13.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="38.73046875" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="8" max="8" style="1" width="9.19921875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="13.265625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="13.265625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="70.73046875" collapsed="true"/>
-    <col min="13" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="30.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="13.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="38.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="9.19921875" style="1" collapsed="1"/>
+    <col min="9" max="9" width="15.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="70.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
@@ -3463,7 +1881,7 @@
         <v>55</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
@@ -3471,7 +1889,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>631</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3494,7 +1912,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>632</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3517,7 +1935,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>633</v>
+        <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3540,7 +1958,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>634</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3563,7 +1981,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>635</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3586,7 +2004,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>636</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -3609,7 +2027,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>637</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -3632,7 +2050,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>638</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -3655,7 +2073,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>639</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -3678,7 +2096,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>640</v>
+        <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -3701,7 +2119,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>641</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -3724,7 +2142,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>642</v>
+        <v>99</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -3747,7 +2165,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>643</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -3770,7 +2188,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>644</v>
+        <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -3793,7 +2211,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>645</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -3813,10 +2231,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>646</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -3845,7 +2263,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>647</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -3871,10 +2289,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>648</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -3903,7 +2321,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>649</v>
+        <v>106</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -3923,10 +2341,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>650</v>
+        <v>107</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -3952,10 +2370,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>651</v>
+        <v>108</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -3984,7 +2402,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>652</v>
+        <v>109</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -4010,7 +2428,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>653</v>
+        <v>110</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -4036,10 +2454,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>654</v>
+        <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -4068,7 +2486,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>655</v>
+        <v>112</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -4094,10 +2512,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>656</v>
+        <v>113</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -4123,7 +2541,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>657</v>
+        <v>114</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -4149,10 +2567,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>658</v>
+        <v>115</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -4178,10 +2596,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>659</v>
+        <v>116</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -4207,10 +2625,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>660</v>
+        <v>117</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -4239,7 +2657,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>661</v>
+        <v>118</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -4259,10 +2677,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>662</v>
+        <v>119</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -4288,10 +2706,10 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>663</v>
+        <v>120</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -4317,10 +2735,10 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>664</v>
+        <v>121</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -4346,7 +2764,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>665</v>
+        <v>122</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -4375,7 +2793,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>666</v>
+        <v>123</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -4401,10 +2819,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>667</v>
+        <v>124</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -4430,10 +2848,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>668</v>
+        <v>125</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -4459,7 +2877,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>669</v>
+        <v>126</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -4488,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>670</v>
+        <v>127</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -4514,10 +2932,10 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>671</v>
+        <v>128</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -4546,7 +2964,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>672</v>
+        <v>129</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -4575,7 +2993,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>673</v>
+        <v>130</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -4595,10 +3013,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>674</v>
+        <v>131</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -4627,7 +3045,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>675</v>
+        <v>132</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -4656,7 +3074,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>676</v>
+        <v>133</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -4679,10 +3097,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>677</v>
+        <v>134</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -4711,7 +3129,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>678</v>
+        <v>135</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -4740,7 +3158,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>679</v>
+        <v>136</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -4766,10 +3184,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>680</v>
+        <v>137</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -4795,7 +3213,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>681</v>
+        <v>138</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -4824,7 +3242,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>682</v>
+        <v>139</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -4844,10 +3262,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>683</v>
+        <v>140</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -4893,7 +3311,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>684</v>
+        <v>141</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -4916,7 +3334,7 @@
         <v>35</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>685</v>
+        <v>142</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -4962,7 +3380,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>686</v>
+        <v>143</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -4985,7 +3403,7 @@
         <v>35</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>687</v>
+        <v>144</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -5031,7 +3449,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>688</v>
+        <v>145</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -5040,7 +3458,7 @@
         <v>16</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>63</v>
@@ -5057,7 +3475,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>689</v>
+        <v>146</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -5066,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>56</v>
@@ -5080,10 +3498,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>690</v>
+        <v>147</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -5092,7 +3510,7 @@
         <v>16</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>37</v>
@@ -5119,12 +3537,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="23" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -5226,12 +3644,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -5259,7 +3677,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>691</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -5276,10 +3694,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>692</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -5296,10 +3714,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>693</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -5319,7 +3737,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>694</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -5336,10 +3754,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>695</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -5356,10 +3774,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>696</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -5376,10 +3794,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>697</v>
+        <v>155</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -5396,10 +3814,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>698</v>
+        <v>156</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -5424,12 +3842,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -5454,10 +3872,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>584</v>
+        <v>157</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -5474,10 +3892,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -5494,10 +3912,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>586</v>
+        <v>159</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -5514,10 +3932,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>587</v>
+        <v>160</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -5534,10 +3952,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>588</v>
+        <v>161</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -5562,12 +3980,12 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -5592,7 +4010,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>536</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
